--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_165_R17.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_165_R17.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8925</v>
+        <v>3.9886</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9746</v>
+        <v>3.6338</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.3548</v>
       </c>
       <c r="G2" t="n">
         <v>4.3988</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2823</v>
+        <v>0.3785</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8837</v>
+        <v>0.543</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6014</v>
+        <v>-0.1645</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7886</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5289</v>
+        <v>3.7147</v>
       </c>
       <c r="E3" t="n">
-        <v>2.148</v>
+        <v>2.5019</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3809</v>
+        <v>1.2129</v>
       </c>
       <c r="G3" t="n">
         <v>0.6671</v>
@@ -688,13 +688,13 @@
         <v>0.4639</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2535</v>
+        <v>0.4393</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0668</v>
+        <v>0.2871</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3203</v>
+        <v>0.1522</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. POIRIER</t>
+          <t>R. BEAUBOIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.781</v>
+        <v>2.3079</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9261</v>
+        <v>3.8618</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8549</v>
+        <v>-1.5539</v>
       </c>
       <c r="G4" t="n">
-        <v>2.447</v>
+        <v>5.8313</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2892</v>
+        <v>2.5689</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1578</v>
+        <v>3.2623</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9793</v>
+        <v>5.0278</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8688</v>
+        <v>2.7091</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1104</v>
+        <v>2.3187</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4678</v>
+        <v>0.8035</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5796</v>
+        <v>-0.1401</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0474</v>
+        <v>0.9436</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0299</v>
+        <v>-1.147</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0351</v>
+        <v>-0.5423</v>
       </c>
       <c r="U4" t="n">
-        <v>0.065</v>
+        <v>-0.6047</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. BEAUBOIS</t>
+          <t>V. POIRIER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5769</v>
+        <v>1.5959</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4333</v>
+        <v>0.8082</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8564</v>
+        <v>0.7877</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8313</v>
+        <v>2.447</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5689</v>
+        <v>1.2892</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2623</v>
+        <v>1.1578</v>
       </c>
       <c r="J5" t="n">
-        <v>5.0278</v>
+        <v>1.9793</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7091</v>
+        <v>1.8688</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3187</v>
+        <v>0.1104</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8035</v>
+        <v>0.4678</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1401</v>
+        <v>-0.5796</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9436</v>
+        <v>1.0474</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.878</v>
+        <v>-0.1553</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9709</v>
+        <v>-0.1531</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9071</v>
+        <v>-0.0022</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.6805</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9615</v>
+        <v>1.178</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8256</v>
+        <v>0.975</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1358</v>
+        <v>0.203</v>
       </c>
       <c r="G6" t="n">
         <v>2.187</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0606</v>
+        <v>0.2772</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0553</v>
+        <v>0.2047</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0053</v>
+        <v>0.0725</v>
       </c>
       <c r="V6" t="n">
         <v>-1.7501</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5707</v>
+        <v>-0.7477</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4666</v>
+        <v>-0.274</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1041</v>
+        <v>-0.4738</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6459</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1294</v>
+        <v>0.9524</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3541</v>
+        <v>0.5467</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7754</v>
+        <v>0.4057</v>
       </c>
       <c r="V7" t="n">
         <v>-1.7501</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1092</v>
+        <v>-1.5633</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8461</v>
+        <v>-1.5355</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.263</v>
+        <v>-0.0278</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1119</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9045</v>
+        <v>-0.3587</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4323</v>
+        <v>-0.1217</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4722</v>
+        <v>-0.237</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7886</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3026</v>
+        <v>-2.4124</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1661</v>
+        <v>-1.9735</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1364</v>
+        <v>-0.4389</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0769</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3159</v>
+        <v>-0.4257</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4481</v>
+        <v>-0.2555</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1322</v>
+        <v>-0.1702</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6778999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3869</v>
+        <v>-3.2518</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5368</v>
+        <v>-3.3009</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1499</v>
+        <v>0.0491</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6052</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7121</v>
+        <v>-0.577</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>-0.3615</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1147</v>
+        <v>-0.2155</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.703</v>
+        <v>-3.4768</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.852</v>
+        <v>-3.6594</v>
       </c>
       <c r="F11" t="n">
-        <v>0.149</v>
+        <v>0.1826</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8134</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2702</v>
+        <v>0.4964</v>
       </c>
       <c r="T11" t="n">
-        <v>0.13</v>
+        <v>0.3227</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1401</v>
+        <v>0.1737</v>
       </c>
       <c r="V11" t="n">
         <v>1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1141</v>
+        <v>-4.032</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0245</v>
+        <v>-3.8751</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0896</v>
+        <v>-0.1568</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1183</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7486</v>
+        <v>-0.6664</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5579</v>
+        <v>-0.4086</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1906</v>
+        <v>-0.2579</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.445699999999999</v>
+        <v>-2.698899999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5845</v>
+        <v>-2.837700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1388999999999999</v>
+        <v>0.1389</v>
       </c>
       <c r="G13" t="n">
         <v>4.159599999999999</v>
@@ -1468,13 +1468,13 @@
         <v>9.2783</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5332</v>
+        <v>-0.7862999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6855</v>
+        <v>0.0615</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8477000000000002</v>
+        <v>-0.8479000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-3.752699999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.952</v>
+        <v>4.9604</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6039</v>
+        <v>5.2017</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3481</v>
+        <v>-0.2412</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2659</v>
+        <v>2.4629</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6587</v>
+        <v>3.0116</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.3928</v>
+        <v>-0.5487</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1666</v>
+        <v>3.1992</v>
       </c>
       <c r="K14" t="n">
-        <v>3.452</v>
+        <v>3.0052</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.2854</v>
+        <v>0.1939</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.7363</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2067</v>
+        <v>0.0063</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1074</v>
+        <v>-0.7426</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9386</v>
+        <v>0.1032</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3135</v>
+        <v>0.0358</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6251</v>
+        <v>0.0674</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3558</v>
+        <v>1.4665</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3558</v>
+        <v>3.3584</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6187</v>
+        <v>3.8124</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3196</v>
+        <v>2.5423</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7009</v>
+        <v>1.2701</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4629</v>
+        <v>0.2659</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0116</v>
+        <v>3.6587</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5487</v>
+        <v>-3.3928</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1992</v>
+        <v>1.1666</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0052</v>
+        <v>3.452</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1939</v>
+        <v>-2.2854</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7363</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0063</v>
+        <v>0.2067</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7426</v>
+        <v>-1.1074</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2385</v>
+        <v>0.7991</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1537</v>
+        <v>0.2519</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3923</v>
+        <v>0.5472</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4665</v>
+        <v>1.3558</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3584</v>
+        <v>1.3558</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>S. SANLI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.351</v>
+        <v>2.3116</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6626</v>
+        <v>1.0829</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6884</v>
+        <v>1.2286</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0592</v>
+        <v>1.0565</v>
       </c>
       <c r="H16" t="n">
-        <v>0.377</v>
+        <v>0.4274</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3178</v>
+        <v>0.6291</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1918</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9782</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1326</v>
+        <v>0.4179</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6012</v>
+        <v>-0.2112</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4685</v>
+        <v>0.6291</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>1.364</v>
+        <v>0.7912</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7027</v>
+        <v>0.4443</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3387</v>
+        <v>0.3468</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. SANLI</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7668</v>
+        <v>2.1042</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7291</v>
+        <v>1.7648</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0378</v>
+        <v>0.3394</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0565</v>
+        <v>-0.8653</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4274</v>
+        <v>-0.3735</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6291</v>
+        <v>-0.4918</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6385999999999999</v>
+        <v>-0.8364</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6385999999999999</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4179</v>
+        <v>-0.0289</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2112</v>
+        <v>-0.2866</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6291</v>
+        <v>0.2578</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2464</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0905</v>
+        <v>0.4052</v>
       </c>
       <c r="U17" t="n">
-        <v>0.156</v>
+        <v>0.2807</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5728</v>
+        <v>1.881</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0089</v>
+        <v>0.8909</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5639</v>
+        <v>0.9901</v>
       </c>
       <c r="G18" t="n">
         <v>0.218</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2689</v>
+        <v>0.0393</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1098</v>
+        <v>-0.2278</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.159</v>
+        <v>0.2671</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2215</v>
+        <v>1.7999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7033</v>
+        <v>0.719</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5182</v>
+        <v>1.0809</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8653</v>
+        <v>0.0592</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3735</v>
+        <v>0.377</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4918</v>
+        <v>-0.3178</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8364</v>
+        <v>0.1918</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.08690000000000001</v>
+        <v>0.9782</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.7863</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0289</v>
+        <v>-0.1326</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2866</v>
+        <v>-0.6012</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2578</v>
+        <v>0.4685</v>
       </c>
       <c r="P19" t="n">
         <v>0.9278</v>
@@ -1936,22 +1936,22 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1968</v>
+        <v>0.8129</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6563</v>
+        <v>0.7591</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4595</v>
+        <v>0.0538</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.428</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3092</v>
+        <v>-0.1898</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.01</v>
+        <v>-0.3638</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3192</v>
+        <v>0.174</v>
       </c>
       <c r="G20" t="n">
         <v>1.21</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5452</v>
+        <v>0.0461</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0351</v>
+        <v>-0.389</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5803</v>
+        <v>0.4351</v>
       </c>
       <c r="V20" t="n">
         <v>-1.214</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.4575</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0423</v>
+        <v>0.2386</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6294</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1129</v>
+        <v>0.4039</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2829</v>
+        <v>-0.047</v>
       </c>
       <c r="U21" t="n">
-        <v>0.17</v>
+        <v>0.4509</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3356</v>
+        <v>-2.094</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2666</v>
+        <v>-2.1486</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.0546</v>
       </c>
       <c r="G22" t="n">
         <v>0.1405</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.127</v>
+        <v>0.3686</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0158</v>
+        <v>0.1338</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1111</v>
+        <v>0.2348</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2836</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7468</v>
+        <v>-4.8203</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.1402</v>
+        <v>-5.3145</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3934</v>
+        <v>0.4942</v>
       </c>
       <c r="G24" t="n">
         <v>-5.3293</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2577</v>
+        <v>-0.3312</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0455</v>
+        <v>-0.2199</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2122</v>
+        <v>-0.1114</v>
       </c>
       <c r="V24" t="n">
         <v>1.0722</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.445599999999999</v>
+        <v>5.018200000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1389000000000005</v>
+        <v>-0.1388999999999996</v>
       </c>
       <c r="F25" t="n">
-        <v>3.5845</v>
+        <v>5.157099999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.159600000000001</v>
+        <v>-4.1596</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6824</v>
+        <v>2.682399999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-6.842199999999999</v>
@@ -2380,7 +2380,7 @@
         <v>-0.9950999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>4.492899999999999</v>
+        <v>4.492900000000001</v>
       </c>
       <c r="L25" t="n">
         <v>-5.488</v>
@@ -2392,7 +2392,7 @@
         <v>-1.8106</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.354100000000001</v>
+        <v>-1.3541</v>
       </c>
       <c r="P25" t="n">
         <v>2.3194</v>
@@ -2404,13 +2404,13 @@
         <v>11.5978</v>
       </c>
       <c r="S25" t="n">
-        <v>1.533100000000001</v>
+        <v>3.1058</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8478999999999994</v>
+        <v>0.8476999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6853000000000002</v>
+        <v>2.2579</v>
       </c>
       <c r="V25" t="n">
         <v>3.7527</v>
